--- a/08_Reports - Доклади - Berichte/Master_Financial_Timeline_Strict/strict_timeline_gaps.xlsx
+++ b/08_Reports - Доклади - Berichte/Master_Financial_Timeline_Strict/strict_timeline_gaps.xlsx
@@ -55,32 +55,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>payroll</t>
+          <t>health insurance</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_TOTALS</t>
+          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month; available payroll rows are blank/low confidence or do not provide explicit totals.</t>
+          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
+          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; Januar 2024; 01.2024; 2024-01</t>
+          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; Januar 2024; 01.2024; 2024-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
         </is>
       </c>
     </row>
@@ -92,32 +92,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>health insurance</t>
+          <t>operating cost</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
+          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month; ambiguous health rows were excluded from totals.</t>
+          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
+          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; Januar 2024; 01.2024; 2024-01</t>
+          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Januar 2024; 01.2024; 2024-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
         </is>
       </c>
     </row>
@@ -129,69 +129,69 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>operating cost</t>
+          <t>Enrico</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
+          <t>MISSING_ENRICO_EVIDENCE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month; generic invoice totals are not accepted as obligations.</t>
+          <t>No strict included Enrico revenue/deduction/refund evidence rows exist for this month.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
+          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Januar 2024; 01.2024; 2024-01</t>
+          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; Januar 2024; 01.2024; 2024-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
+          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Enrico</t>
+          <t>health insurance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MISSING_ENRICO_EVIDENCE</t>
+          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>No strict included Enrico revenue/deduction/refund evidence rows exist for this month.</t>
+          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
+          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; Januar 2024; 01.2024; 2024-01</t>
+          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; Februar 2024; 02.2024; 2024-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
         </is>
       </c>
     </row>
@@ -203,32 +203,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>payroll</t>
+          <t>operating cost</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_TOTALS</t>
+          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month; available payroll rows are blank/low confidence or do not provide explicit totals.</t>
+          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
+          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; Februar 2024; 02.2024; 2024-02</t>
+          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Februar 2024; 02.2024; 2024-02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
         </is>
       </c>
     </row>
@@ -240,106 +240,106 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>health insurance</t>
+          <t>Enrico</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
+          <t>MISSING_ENRICO_EVIDENCE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month; ambiguous health rows were excluded from totals.</t>
+          <t>No strict included Enrico revenue/deduction/refund evidence rows exist for this month.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
+          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; Februar 2024; 02.2024; 2024-02</t>
+          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; Februar 2024; 02.2024; 2024-02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
+          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>operating cost</t>
+          <t>health insurance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
+          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month; generic invoice totals are not accepted as obligations.</t>
+          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
+          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Februar 2024; 02.2024; 2024-02</t>
+          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; M?rz 2024; 03.2024; 2024-03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Enrico</t>
+          <t>operating cost</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MISSING_ENRICO_EVIDENCE</t>
+          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>No strict included Enrico revenue/deduction/refund evidence rows exist for this month.</t>
+          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
+          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; Februar 2024; 02.2024; 2024-02</t>
+          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; M?rz 2024; 03.2024; 2024-03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
         </is>
       </c>
     </row>
@@ -351,143 +351,143 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>payroll</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_TOTALS</t>
+          <t>MISSING_STRICT_TAX_STATUS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month; available payroll rows are blank/low confidence or do not provide explicit totals.</t>
+          <t>No strict included tax due/paid/unpaid rows exist for this month.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
+          <t>Tax notice or payment confirmation clearly identifying creditor, tax type, amount due/paid/unpaid, and period.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; M?rz 2024; 03.2024; 2024-03</t>
+          <t>Finanzamt; Umsatzsteuer; UStVA; Lohnsteuer; Einkommensteuer; Gewerbesteuer; Stadt Chemnitz; Steuerbescheid; Vorauszahlung; f?llig; Zahlung; M?rz 2024; 03.2024; 2024-03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/05_Taxes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>health insurance</t>
+          <t>payroll</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
+          <t>MISSING_STRICT_TOTALS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month; ambiguous health rows were excluded from totals.</t>
+          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
+          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; M?rz 2024; 03.2024; 2024-03</t>
+          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; April 2024; 04.2024; 2024-04</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>operating cost</t>
+          <t>health insurance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
+          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month; generic invoice totals are not accepted as obligations.</t>
+          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
+          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; M?rz 2024; 03.2024; 2024-03</t>
+          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; April 2024; 04.2024; 2024-04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>tax</t>
+          <t>operating cost</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_TAX_STATUS</t>
+          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>No strict included tax due/paid/unpaid rows exist for this month; generic tax amounts or unclear bank movements were excluded.</t>
+          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tax notice or payment confirmation clearly identifying creditor, tax type, amount due/paid/unpaid, and period.</t>
+          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Finanzamt; Umsatzsteuer; UStVA; Lohnsteuer; Einkommensteuer; Gewerbesteuer; Stadt Chemnitz; Steuerbescheid; Vorauszahlung; f?llig; Zahlung; M?rz 2024; 03.2024; 2024-03</t>
+          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; April 2024; 04.2024; 2024-04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/05_Taxes</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
         </is>
       </c>
     </row>
@@ -499,143 +499,143 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>payroll</t>
+          <t>Enrico</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_TOTALS</t>
+          <t>MISSING_ENRICO_EVIDENCE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month; available payroll rows are blank/low confidence or do not provide explicit totals.</t>
+          <t>No strict included Enrico revenue/deduction/refund evidence rows exist for this month.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
+          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; April 2024; 04.2024; 2024-04</t>
+          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; April 2024; 04.2024; 2024-04</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
+          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>health insurance</t>
+          <t>payroll</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
+          <t>MISSING_STRICT_TOTALS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month; ambiguous health rows were excluded from totals.</t>
+          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
+          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; April 2024; 04.2024; 2024-04</t>
+          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; Mai 2024; 05.2024; 2024-05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>operating cost</t>
+          <t>health insurance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
+          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month; generic invoice totals are not accepted as obligations.</t>
+          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
+          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; April 2024; 04.2024; 2024-04</t>
+          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; Mai 2024; 05.2024; 2024-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Enrico</t>
+          <t>operating cost</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MISSING_ENRICO_EVIDENCE</t>
+          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>No strict included Enrico revenue/deduction/refund evidence rows exist for this month.</t>
+          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
+          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; April 2024; 04.2024; 2024-04</t>
+          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Mai 2024; 05.2024; 2024-05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
         </is>
       </c>
     </row>
@@ -647,76 +647,76 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>payroll</t>
+          <t>Enrico</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_TOTALS</t>
+          <t>MISSING_ENRICO_EVIDENCE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month; available payroll rows are blank/low confidence or do not provide explicit totals.</t>
+          <t>No strict included Enrico revenue/deduction/refund evidence rows exist for this month.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
+          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; Mai 2024; 05.2024; 2024-05</t>
+          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; Mai 2024; 05.2024; 2024-05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
+          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>health insurance</t>
+          <t>payroll</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
+          <t>MISSING_STRICT_TOTALS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month; ambiguous health rows were excluded from totals.</t>
+          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
+          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; Mai 2024; 05.2024; 2024-05</t>
+          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; Juni 2024; 06.2024; 2024-06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month; generic invoice totals are not accepted as obligations.</t>
+          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Mai 2024; 05.2024; 2024-05</t>
+          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Juni 2024; 06.2024; 2024-06</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; Mai 2024; 05.2024; 2024-05</t>
+          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; Juni 2024; 06.2024; 2024-06</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -790,81 +790,81 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>payroll</t>
+          <t>operating cost</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_TOTALS</t>
+          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month; available payroll rows are blank/low confidence or do not provide explicit totals.</t>
+          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
+          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; Juni 2024; 06.2024; 2024-06</t>
+          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Juli 2024; 07.2024; 2024-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>health insurance</t>
+          <t>Enrico</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
+          <t>MISSING_ENRICO_EVIDENCE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month; ambiguous health rows were excluded from totals.</t>
+          <t>No strict included Enrico revenue/deduction/refund evidence rows exist for this month.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
+          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; Juni 2024; 06.2024; 2024-06</t>
+          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; Juli 2024; 07.2024; 2024-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
+          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month; generic invoice totals are not accepted as obligations.</t>
+          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Juni 2024; 06.2024; 2024-06</t>
+          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; August 2024; 08.2024; 2024-08</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -911,12 +911,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MISSING_ENRICO_EVIDENCE</t>
+          <t>PARTIAL_ENRICO_NO_MAIN_GUTSCHRIFT</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>No strict included Enrico revenue/deduction/refund evidence rows exist for this month.</t>
+          <t>Enrico evidence exists, but no strict included REVENUE/main Gutschrift row exists for this month.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; Juni 2024; 06.2024; 2024-06</t>
+          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; August 2024; 08.2024; 2024-08</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -938,7 +938,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month; available payroll rows are blank/low confidence or do not provide explicit totals.</t>
+          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; Juli 2024; 07.2024; 2024-07</t>
+          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; September 2024; 09.2024; 2024-09</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -975,44 +975,44 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>health insurance</t>
+          <t>operating cost</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
+          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month; ambiguous health rows were excluded from totals.</t>
+          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
+          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; Juli 2024; 07.2024; 2024-07</t>
+          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; September 2024; 09.2024; 2024-09</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month; generic invoice totals are not accepted as obligations.</t>
+          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Juli 2024; 07.2024; 2024-07</t>
+          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Oktober 2024; 10.2024; 2024-10</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1049,118 +1049,118 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Enrico</t>
+          <t>payroll</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MISSING_ENRICO_EVIDENCE</t>
+          <t>MISSING_STRICT_TOTALS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>No strict included Enrico revenue/deduction/refund evidence rows exist for this month.</t>
+          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
+          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; Juli 2024; 07.2024; 2024-07</t>
+          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; November 2024; 11.2024; 2024-11</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>payroll</t>
+          <t>operating cost</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_TOTALS</t>
+          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month; available payroll rows are blank/low confidence or do not provide explicit totals.</t>
+          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
+          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; August 2024; 08.2024; 2024-08</t>
+          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; November 2024; 11.2024; 2024-11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>health insurance</t>
+          <t>payroll</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
+          <t>MISSING_STRICT_TOTALS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month; ambiguous health rows were excluded from totals.</t>
+          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
+          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; August 2024; 08.2024; 2024-08</t>
+          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; Dezember 2024; 12.2024; 2024-12</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month; generic invoice totals are not accepted as obligations.</t>
+          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; August 2024; 08.2024; 2024-08</t>
+          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Dezember 2024; 12.2024; 2024-12</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1197,81 +1197,81 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>tax</t>
+          <t>payroll</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_TAX_STATUS</t>
+          <t>MISSING_STRICT_TOTALS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>No strict included tax due/paid/unpaid rows exist for this month; generic tax amounts or unclear bank movements were excluded.</t>
+          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tax notice or payment confirmation clearly identifying creditor, tax type, amount due/paid/unpaid, and period.</t>
+          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Finanzamt; Umsatzsteuer; UStVA; Lohnsteuer; Einkommensteuer; Gewerbesteuer; Stadt Chemnitz; Steuerbescheid; Vorauszahlung; f?llig; Zahlung; August 2024; 08.2024; 2024-08</t>
+          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; Januar 2025; 01.2025; 2025-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/05_Taxes</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Enrico</t>
+          <t>operating cost</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PARTIAL_ENRICO_NO_MAIN_GUTSCHRIFT</t>
+          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Enrico evidence exists, but no strict included REVENUE/main Gutschrift row exists for this month.</t>
+          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
+          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; August 2024; 08.2024; 2024-08</t>
+          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Januar 2025; 01.2025; 2025-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month; available payroll rows are blank/low confidence or do not provide explicit totals.</t>
+          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; September 2024; 09.2024; 2024-09</t>
+          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; Februar 2025; 02.2025; 2025-02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1308,155 +1308,155 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>health insurance</t>
+          <t>operating cost</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
+          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month; ambiguous health rows were excluded from totals.</t>
+          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
+          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; September 2024; 09.2024; 2024-09</t>
+          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Februar 2025; 02.2025; 2025-02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>operating cost</t>
+          <t>payroll</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
+          <t>MISSING_STRICT_TOTALS</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month; generic invoice totals are not accepted as obligations.</t>
+          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
+          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; September 2024; 09.2024; 2024-09</t>
+          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; M?rz 2025; 03.2025; 2025-03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>payroll</t>
+          <t>health insurance</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_TOTALS</t>
+          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month; available payroll rows are blank/low confidence or do not provide explicit totals.</t>
+          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
+          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; Oktober 2024; 10.2024; 2024-10</t>
+          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; M?rz 2025; 03.2025; 2025-03</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>health insurance</t>
+          <t>operating cost</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
+          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month; ambiguous health rows were excluded from totals.</t>
+          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
+          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; Oktober 2024; 10.2024; 2024-10</t>
+          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; M?rz 2025; 03.2025; 2025-03</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month; generic invoice totals are not accepted as obligations.</t>
+          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Oktober 2024; 10.2024; 2024-10</t>
+          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; April 2025; 04.2025; 2025-04</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1493,81 +1493,81 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>payroll</t>
+          <t>Enrico</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_TOTALS</t>
+          <t>PARTIAL_ENRICO_NO_MAIN_GUTSCHRIFT</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month; available payroll rows are blank/low confidence or do not provide explicit totals.</t>
+          <t>Enrico evidence exists, but no strict included REVENUE/main Gutschrift row exists for this month.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
+          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; November 2024; 11.2024; 2024-11</t>
+          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; April 2025; 04.2025; 2025-04</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
+          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>health insurance</t>
+          <t>operating cost</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
+          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month; ambiguous health rows were excluded from totals.</t>
+          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
+          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; November 2024; 11.2024; 2024-11</t>
+          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Mai 2025; 05.2025; 2025-05</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month; generic invoice totals are not accepted as obligations.</t>
+          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; November 2024; 11.2024; 2024-11</t>
+          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Juni 2025; 06.2025; 2025-06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1604,997 +1604,35 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>payroll</t>
+          <t>Enrico</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_TOTALS</t>
+          <t>MISSING_ENRICO_EVIDENCE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month; available payroll rows are blank/low confidence or do not provide explicit totals.</t>
+          <t>No strict included Enrico revenue/deduction/refund evidence rows exist for this month.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
+          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; Dezember 2024; 12.2024; 2024-12</t>
+          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; Juni 2025; 06.2025; 2025-06</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2024-12</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>health insurance</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month; ambiguous health rows were excluded from totals.</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; Dezember 2024; 12.2024; 2024-12</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2024-12</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>operating cost</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month; generic invoice totals are not accepted as obligations.</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Dezember 2024; 12.2024; 2024-12</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>payroll</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_TOTALS</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month; available payroll rows are blank/low confidence or do not provide explicit totals.</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; Januar 2025; 01.2025; 2025-01</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>health insurance</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month; ambiguous health rows were excluded from totals.</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; Januar 2025; 01.2025; 2025-01</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>operating cost</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month; generic invoice totals are not accepted as obligations.</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Januar 2025; 01.2025; 2025-01</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2025-02</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>payroll</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_TOTALS</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month; available payroll rows are blank/low confidence or do not provide explicit totals.</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; Februar 2025; 02.2025; 2025-02</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2025-02</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>health insurance</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month; ambiguous health rows were excluded from totals.</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; Februar 2025; 02.2025; 2025-02</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2025-02</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>operating cost</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month; generic invoice totals are not accepted as obligations.</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Februar 2025; 02.2025; 2025-02</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>payroll</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_TOTALS</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month; available payroll rows are blank/low confidence or do not provide explicit totals.</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; M?rz 2025; 03.2025; 2025-03</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>health insurance</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month; ambiguous health rows were excluded from totals.</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; M?rz 2025; 03.2025; 2025-03</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>operating cost</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month; generic invoice totals are not accepted as obligations.</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; M?rz 2025; 03.2025; 2025-03</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>tax</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_TAX_STATUS</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>No strict included tax due/paid/unpaid rows exist for this month; generic tax amounts or unclear bank movements were excluded.</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Tax notice or payment confirmation clearly identifying creditor, tax type, amount due/paid/unpaid, and period.</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Finanzamt; Umsatzsteuer; UStVA; Lohnsteuer; Einkommensteuer; Gewerbesteuer; Stadt Chemnitz; Steuerbescheid; Vorauszahlung; f?llig; Zahlung; M?rz 2025; 03.2025; 2025-03</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/05_Taxes</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>payroll</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_TOTALS</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month; available payroll rows are blank/low confidence or do not provide explicit totals.</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; April 2025; 04.2025; 2025-04</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>health insurance</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month; ambiguous health rows were excluded from totals.</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; April 2025; 04.2025; 2025-04</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>operating cost</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month; generic invoice totals are not accepted as obligations.</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; April 2025; 04.2025; 2025-04</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>tax</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_TAX_STATUS</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>No strict included tax due/paid/unpaid rows exist for this month; generic tax amounts or unclear bank movements were excluded.</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Tax notice or payment confirmation clearly identifying creditor, tax type, amount due/paid/unpaid, and period.</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Finanzamt; Umsatzsteuer; UStVA; Lohnsteuer; Einkommensteuer; Gewerbesteuer; Stadt Chemnitz; Steuerbescheid; Vorauszahlung; f?llig; Zahlung; April 2025; 04.2025; 2025-04</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/05_Taxes</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Enrico</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>PARTIAL_ENRICO_NO_MAIN_GUTSCHRIFT</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Enrico evidence exists, but no strict included REVENUE/main Gutschrift row exists for this month.</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; April 2025; 04.2025; 2025-04</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>payroll</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_TOTALS</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month; available payroll rows are blank/low confidence or do not provide explicit totals.</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; Mai 2025; 05.2025; 2025-05</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>health insurance</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month; ambiguous health rows were excluded from totals.</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; Mai 2025; 05.2025; 2025-05</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>operating cost</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month; generic invoice totals are not accepted as obligations.</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Mai 2025; 05.2025; 2025-05</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>tax</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_TAX_STATUS</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>No strict included tax due/paid/unpaid rows exist for this month; generic tax amounts or unclear bank movements were excluded.</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Tax notice or payment confirmation clearly identifying creditor, tax type, amount due/paid/unpaid, and period.</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Finanzamt; Umsatzsteuer; UStVA; Lohnsteuer; Einkommensteuer; Gewerbesteuer; Stadt Chemnitz; Steuerbescheid; Vorauszahlung; f?llig; Zahlung; Mai 2025; 05.2025; 2025-05</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/05_Taxes</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>payroll</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_TOTALS</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month; available payroll rows are blank/low confidence or do not provide explicit totals.</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; Juni 2025; 06.2025; 2025-06</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>health insurance</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month; ambiguous health rows were excluded from totals.</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; Juni 2025; 06.2025; 2025-06</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>operating cost</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month; generic invoice totals are not accepted as obligations.</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Juni 2025; 06.2025; 2025-06</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>tax</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_TAX_STATUS</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>No strict included tax due/paid/unpaid rows exist for this month; generic tax amounts or unclear bank movements were excluded.</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Tax notice or payment confirmation clearly identifying creditor, tax type, amount due/paid/unpaid, and period.</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Finanzamt; Umsatzsteuer; UStVA; Lohnsteuer; Einkommensteuer; Gewerbesteuer; Stadt Chemnitz; Steuerbescheid; Vorauszahlung; f?llig; Zahlung; Juni 2025; 06.2025; 2025-06</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/05_Taxes</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Enrico</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>MISSING_ENRICO_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>No strict included Enrico revenue/deduction/refund evidence rows exist for this month.</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; Juni 2025; 06.2025; 2025-06</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
         <is>
           <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
         </is>

--- a/08_Reports - Доклади - Berichte/Master_Financial_Timeline_Strict/strict_timeline_gaps.xlsx
+++ b/08_Reports - Доклади - Berichte/Master_Financial_Timeline_Strict/strict_timeline_gaps.xlsx
@@ -92,69 +92,69 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>operating cost</t>
+          <t>Enrico</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
+          <t>MISSING_ENRICO_EVIDENCE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
+          <t>No strict included Enrico revenue/deduction/refund evidence rows exist for this month.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
+          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Januar 2024; 01.2024; 2024-01</t>
+          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; Januar 2024; 01.2024; 2024-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
+          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Enrico</t>
+          <t>health insurance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MISSING_ENRICO_EVIDENCE</t>
+          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>No strict included Enrico revenue/deduction/refund evidence rows exist for this month.</t>
+          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
+          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; Januar 2024; 01.2024; 2024-01</t>
+          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; Februar 2024; 02.2024; 2024-02</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
         </is>
       </c>
     </row>
@@ -166,224 +166,224 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>health insurance</t>
+          <t>Enrico</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
+          <t>MISSING_ENRICO_EVIDENCE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month.</t>
+          <t>No strict included Enrico revenue/deduction/refund evidence rows exist for this month.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
+          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; Februar 2024; 02.2024; 2024-02</t>
+          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; Februar 2024; 02.2024; 2024-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
+          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>operating cost</t>
+          <t>health insurance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
+          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
+          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
+          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Februar 2024; 02.2024; 2024-02</t>
+          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; M?rz 2024; 03.2024; 2024-03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Enrico</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MISSING_ENRICO_EVIDENCE</t>
+          <t>MISSING_STRICT_TAX_STATUS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>No strict included Enrico revenue/deduction/refund evidence rows exist for this month.</t>
+          <t>No strict included tax due/paid/unpaid rows exist for this month.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
+          <t>Tax notice or payment confirmation clearly identifying creditor, tax type, amount due/paid/unpaid, and period.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; Februar 2024; 02.2024; 2024-02</t>
+          <t>Finanzamt; Umsatzsteuer; UStVA; Lohnsteuer; Einkommensteuer; Gewerbesteuer; Stadt Chemnitz; Steuerbescheid; Vorauszahlung; f?llig; Zahlung; M?rz 2024; 03.2024; 2024-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/05_Taxes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>health insurance</t>
+          <t>payroll</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
+          <t>MISSING_STRICT_TOTALS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month.</t>
+          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
+          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; M?rz 2024; 03.2024; 2024-03</t>
+          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; April 2024; 04.2024; 2024-04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>operating cost</t>
+          <t>health insurance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
+          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
+          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
+          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; M?rz 2024; 03.2024; 2024-03</t>
+          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; April 2024; 04.2024; 2024-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>tax</t>
+          <t>Enrico</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_TAX_STATUS</t>
+          <t>MISSING_ENRICO_EVIDENCE</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>No strict included tax due/paid/unpaid rows exist for this month.</t>
+          <t>No strict included Enrico revenue/deduction/refund evidence rows exist for this month.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tax notice or payment confirmation clearly identifying creditor, tax type, amount due/paid/unpaid, and period.</t>
+          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Finanzamt; Umsatzsteuer; UStVA; Lohnsteuer; Einkommensteuer; Gewerbesteuer; Stadt Chemnitz; Steuerbescheid; Vorauszahlung; f?llig; Zahlung; M?rz 2024; 03.2024; 2024-03</t>
+          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; April 2024; 04.2024; 2024-04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/05_Taxes</t>
+          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -408,7 +408,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; April 2024; 04.2024; 2024-04</t>
+          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; Mai 2024; 05.2024; 2024-05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -420,7 +420,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -445,7 +445,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; April 2024; 04.2024; 2024-04</t>
+          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; Mai 2024; 05.2024; 2024-05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -457,229 +457,229 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>operating cost</t>
+          <t>Enrico</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
+          <t>MISSING_ENRICO_EVIDENCE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
+          <t>No strict included Enrico revenue/deduction/refund evidence rows exist for this month.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
+          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; April 2024; 04.2024; 2024-04</t>
+          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; Mai 2024; 05.2024; 2024-05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
+          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Enrico</t>
+          <t>payroll</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MISSING_ENRICO_EVIDENCE</t>
+          <t>MISSING_STRICT_TOTALS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>No strict included Enrico revenue/deduction/refund evidence rows exist for this month.</t>
+          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
+          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; April 2024; 04.2024; 2024-04</t>
+          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; Juni 2024; 06.2024; 2024-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>payroll</t>
+          <t>Enrico</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_TOTALS</t>
+          <t>MISSING_ENRICO_EVIDENCE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month.</t>
+          <t>No strict included Enrico revenue/deduction/refund evidence rows exist for this month.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
+          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; Mai 2024; 05.2024; 2024-05</t>
+          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; Juni 2024; 06.2024; 2024-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
+          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>health insurance</t>
+          <t>Enrico</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
+          <t>MISSING_ENRICO_EVIDENCE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month.</t>
+          <t>No strict included Enrico revenue/deduction/refund evidence rows exist for this month.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
+          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; Mai 2024; 05.2024; 2024-05</t>
+          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; Juli 2024; 07.2024; 2024-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
+          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>operating cost</t>
+          <t>Enrico</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
+          <t>PARTIAL_ENRICO_NO_MAIN_GUTSCHRIFT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
+          <t>Enrico evidence exists, but no strict included REVENUE/main Gutschrift row exists for this month.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
+          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Mai 2024; 05.2024; 2024-05</t>
+          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; August 2024; 08.2024; 2024-08</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
+          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Enrico</t>
+          <t>payroll</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MISSING_ENRICO_EVIDENCE</t>
+          <t>MISSING_STRICT_TOTALS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>No strict included Enrico revenue/deduction/refund evidence rows exist for this month.</t>
+          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
+          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; Mai 2024; 05.2024; 2024-05</t>
+          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; September 2024; 09.2024; 2024-09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; Juni 2024; 06.2024; 2024-06</t>
+          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; November 2024; 11.2024; 2024-11</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -716,192 +716,192 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>operating cost</t>
+          <t>payroll</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
+          <t>MISSING_STRICT_TOTALS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
+          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
+          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Juni 2024; 06.2024; 2024-06</t>
+          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; Dezember 2024; 12.2024; 2024-12</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Enrico</t>
+          <t>payroll</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MISSING_ENRICO_EVIDENCE</t>
+          <t>MISSING_STRICT_TOTALS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>No strict included Enrico revenue/deduction/refund evidence rows exist for this month.</t>
+          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
+          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; Juni 2024; 06.2024; 2024-06</t>
+          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; Januar 2025; 01.2025; 2025-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>operating cost</t>
+          <t>payroll</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
+          <t>MISSING_STRICT_TOTALS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
+          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
+          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Juli 2024; 07.2024; 2024-07</t>
+          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; Februar 2025; 02.2025; 2025-02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Enrico</t>
+          <t>payroll</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MISSING_ENRICO_EVIDENCE</t>
+          <t>MISSING_STRICT_TOTALS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>No strict included Enrico revenue/deduction/refund evidence rows exist for this month.</t>
+          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
+          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; Juli 2024; 07.2024; 2024-07</t>
+          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; M?rz 2025; 03.2025; 2025-03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>operating cost</t>
+          <t>health insurance</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
+          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
+          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
+          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; August 2024; 08.2024; 2024-08</t>
+          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; M?rz 2025; 03.2025; 2025-03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
+          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; August 2024; 08.2024; 2024-08</t>
+          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; April 2025; 04.2025; 2025-04</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -938,44 +938,44 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>payroll</t>
+          <t>Enrico</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_TOTALS</t>
+          <t>MISSING_ENRICO_EVIDENCE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month.</t>
+          <t>No strict included Enrico revenue/deduction/refund evidence rows exist for this month.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
+          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; September 2024; 09.2024; 2024-09</t>
+          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; Juni 2025; 06.2025; 2025-06</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
+          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -990,17 +990,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
+          <t>Operating evidence may exist, but no strict due/paid/unpaid operating amount is available. Unknown invoice totals are excluded from totals.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
+          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; September 2024; 09.2024; 2024-09</t>
+          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; 2025-04</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1012,7 +1012,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1027,17 +1027,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
+          <t>Operating evidence may exist, but no strict due/paid/unpaid operating amount is available. Unknown invoice totals are excluded from totals.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
+          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Oktober 2024; 10.2024; 2024-10</t>
+          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; 2025-05</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1049,592 +1049,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>payroll</t>
+          <t>operating cost</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MISSING_STRICT_TOTALS</t>
+          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month.</t>
+          <t>Operating evidence may exist, but no strict due/paid/unpaid operating amount is available. Unknown invoice totals are excluded from totals.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
+          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; November 2024; 11.2024; 2024-11</t>
+          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; 2025-06</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2024-11</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>operating cost</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; November 2024; 11.2024; 2024-11</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
           <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2024-12</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>payroll</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_TOTALS</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month.</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; Dezember 2024; 12.2024; 2024-12</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2024-12</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>operating cost</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Dezember 2024; 12.2024; 2024-12</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>payroll</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_TOTALS</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month.</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; Januar 2025; 01.2025; 2025-01</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>operating cost</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Januar 2025; 01.2025; 2025-01</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2025-02</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>payroll</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_TOTALS</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month.</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; Februar 2025; 02.2025; 2025-02</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2025-02</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>operating cost</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Februar 2025; 02.2025; 2025-02</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>payroll</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_TOTALS</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>No strict included PAYROLL_BRUTTO or PAYROLL_NETTO rows exist for this month.</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Monthly payroll summary showing explicit Brutto and Netto totals; Lohnjournal or Lohnauswertung for the month.</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Lohnauswertung; Lohnjournal; Brutto Netto; Brutto_Netto; Entgeltabrechnung; Gehaltsabrechnung; payroll; Lohnabrechnung; M?rz 2025; 03.2025; 2025-03</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/02_Payroll</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>health insurance</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_STATUS_AMOUNTS</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>No strict included health insurance due/paid/unpaid/late-fee rows exist for this month.</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Krankenkasse Beitragsnachweis/payment statement showing due, paid, unpaid balance, and late fees separately.</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Beitragsnachweis; Krankenkasse; AOK; TK; KKH; Barmer; DAK; BKK; IKK; VIACTIV; Unbedenklichkeitsbescheinigung; Beitragsr?ckstand; Sozialversicherungsbeitr?ge; M?rz 2025; 03.2025; 2025-03</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/04_Health_Insurance</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>operating cost</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; M?rz 2025; 03.2025; 2025-03</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>operating cost</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; April 2025; 04.2025; 2025-04</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Enrico</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>PARTIAL_ENRICO_NO_MAIN_GUTSCHRIFT</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Enrico evidence exists, but no strict included REVENUE/main Gutschrift row exists for this month.</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; April 2025; 04.2025; 2025-04</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>operating cost</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Mai 2025; 05.2025; 2025-05</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>operating cost</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>MISSING_STRICT_DUE_PAID_UNPAID</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>No strict included operating cost due/paid/unpaid rows exist for this month.</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Operating cost invoice/payment/open-item document with explicit due, paid, or unpaid status, not only a generic invoice total.</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Tank; Diesel; Kraftstoff; Fahrzeug; Reparatur; Leasing; Versicherung; Miete; Telefon; Buchhaltung; Steuerberatung; Scanner; Rechnung; bezahlt; offen; f?llig; Juni 2025; 06.2025; 2025-06</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Accounting_Organized/08_Operating_Costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Enrico</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>MISSING_ENRICO_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>No strict included Enrico revenue/deduction/refund evidence rows exist for this month.</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Main monthly Gutschrift/Abrechnung plus related deduction/refund invoices for the month.</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Enrico Wei?flog; Sachsenpower; Gutschrift; Abrechnung; Leistungsnachweis; Rechnung; Sendungsverlust; Abschlag Coincident; Scannermiete; R?ckerstattung; Juni 2025; 06.2025; 2025-06</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>00_INBOX - ??????? - Eingang/Enrico or 00_INBOX - ??????? - Eingang/Accounting_Organized/09_Enrico_Forwarded</t>
         </is>
       </c>
     </row>
